--- a/client/tests/fixtures/mini-config/forms/app/pregnancy.xlsx
+++ b/client/tests/fixtures/mini-config/forms/app/pregnancy.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="47">
   <si>
     <t>type</t>
   </si>
@@ -24,9 +24,15 @@
     <t>label::en</t>
   </si>
   <si>
+    <t>label::ne</t>
+  </si>
+  <si>
     <t>calculation</t>
   </si>
   <si>
+    <t>relevant</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -69,9 +75,36 @@
     <t>Last menstrual period</t>
   </si>
   <si>
+    <t>अन्तिम महिनावारी</t>
+  </si>
+  <si>
     <t>yes</t>
   </si>
   <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>lmp_note</t>
+  </si>
+  <si>
+    <t>LMP recorded</t>
+  </si>
+  <si>
+    <t>${lmp_date} != ''</t>
+  </si>
+  <si>
+    <t>select_multiple danger_signs</t>
+  </si>
+  <si>
+    <t>danger_signs</t>
+  </si>
+  <si>
+    <t>Danger signs</t>
+  </si>
+  <si>
+    <t>खतराका लक्षण</t>
+  </si>
+  <si>
     <t>integer</t>
   </si>
   <si>
@@ -82,6 +115,27 @@
   </si>
   <si>
     <t>list_name</t>
+  </si>
+  <si>
+    <t>vaginal_bleeding</t>
+  </si>
+  <si>
+    <t>Vaginal bleeding</t>
+  </si>
+  <si>
+    <t>योनिबाट रक्तस्राव</t>
+  </si>
+  <si>
+    <t>severe_headache</t>
+  </si>
+  <si>
+    <t>Severe headache</t>
+  </si>
+  <si>
+    <t>blurred_vision</t>
+  </si>
+  <si>
+    <t>Blurred vision</t>
   </si>
   <si>
     <t>form_title</t>
@@ -476,10 +530,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,141 +549,241 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -640,18 +794,63 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -667,24 +866,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/client/tests/fixtures/mini-config/forms/app/pregnancy.xlsx
+++ b/client/tests/fixtures/mini-config/forms/app/pregnancy.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="58">
   <si>
     <t>type</t>
   </si>
@@ -105,6 +105,18 @@
     <t>खतराका लक्षण</t>
   </si>
   <si>
+    <t>select_one pass_fail</t>
+  </si>
+  <si>
+    <t>chair_rise</t>
+  </si>
+  <si>
+    <t>Chair rise test</t>
+  </si>
+  <si>
+    <t>कुर्सी उठ्ने परीक्षण</t>
+  </si>
+  <si>
     <t>integer</t>
   </si>
   <si>
@@ -136,6 +148,27 @@
   </si>
   <si>
     <t>Blurred vision</t>
+  </si>
+  <si>
+    <t>pass_fail</t>
+  </si>
+  <si>
+    <t>fail</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>फेल</t>
+  </si>
+  <si>
+    <t>pass</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>पास</t>
   </si>
   <si>
     <t>form_title</t>
@@ -530,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -774,7 +807,7 @@
         <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -783,6 +816,29 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s">
         <v>9</v>
       </c>
     </row>
@@ -794,12 +850,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -816,13 +872,13 @@
         <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -830,10 +886,10 @@
         <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -844,13 +900,41 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -866,24 +950,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
